--- a/output/graficos_dimensiones/comunal_p_basica_a_2018_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_p_basica_a_2018_biobio.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 20:40</t>
+    <t xml:space="preserve">2026-09-09 23:40</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_p_basica_a_2018_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_p_basica_a_2018_biobio.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 23:40</t>
+    <t xml:space="preserve">2026-09-18 10:28</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_p_basica_a_2018_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_p_basica_a_2018_biobio.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 10:28</t>
+    <t xml:space="preserve">2026-09-23 13:00</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_p_basica_a_2018_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_p_basica_a_2018_biobio.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-23 13:00</t>
+    <t xml:space="preserve">2026-10-02 14:18</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_p_basica_a_2018_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_p_basica_a_2018_biobio.xlsx
@@ -84,7 +84,7 @@
     <t xml:space="preserve">San Rosendo</t>
   </si>
   <si>
-    <t xml:space="preserve">Los Alamos</t>
+    <t xml:space="preserve">Los Álamos</t>
   </si>
   <si>
     <t xml:space="preserve">Cabrero</t>
@@ -105,7 +105,7 @@
     <t xml:space="preserve">Curanilahue</t>
   </si>
   <si>
-    <t xml:space="preserve">Los Angeles</t>
+    <t xml:space="preserve">Los Ángeles</t>
   </si>
   <si>
     <t xml:space="preserve">Coronel</t>
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 14:18</t>
+    <t xml:space="preserve">2026-10-04 09:44</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_p_basica_a_2018_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_p_basica_a_2018_biobio.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-04 09:44</t>
+    <t xml:space="preserve">2026-10-05 13:21</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -852,7 +852,7 @@
         <v>2018</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>28.12</v>
+        <v>28.13</v>
       </c>
     </row>
     <row r="19">
